--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>51.751</v>
+        <v>52.04</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,13 +440,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>45.332</v>
+        <v>45.043</v>
       </c>
       <c r="C3">
         <v>1.243</v>
       </c>
       <c r="D3">
-        <v>0.027</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>233.456</v>
+        <v>236.071</v>
       </c>
       <c r="C5">
-        <v>13.142</v>
+        <v>13.45</v>
       </c>
       <c r="D5">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>201.544</v>
+        <v>198.929</v>
       </c>
       <c r="C6">
-        <v>13.142</v>
+        <v>13.45</v>
       </c>
       <c r="D6">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>50.077</v>
+        <v>50.225</v>
       </c>
       <c r="C7">
-        <v>1.863</v>
+        <v>1.942</v>
       </c>
       <c r="D7">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,13 +510,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>49.923</v>
+        <v>49.775</v>
       </c>
       <c r="C8">
-        <v>1.863</v>
+        <v>1.942</v>
       </c>
       <c r="D8">
-        <v>0.037</v>
+        <v>0.039</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>236.071</v>
+        <v>236.349</v>
       </c>
       <c r="C5">
-        <v>13.45</v>
+        <v>13.498</v>
       </c>
       <c r="D5">
         <v>0.057</v>
@@ -482,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>198.929</v>
+        <v>198.651</v>
       </c>
       <c r="C6">
-        <v>13.45</v>
+        <v>13.498</v>
       </c>
       <c r="D6">
         <v>0.068</v>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,13 +426,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>52.04</v>
+        <v>52.463</v>
       </c>
       <c r="C2">
         <v>1.487</v>
       </c>
       <c r="D2">
-        <v>0.029</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>45.043</v>
+        <v>44.62</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>236.349</v>
+        <v>239.321</v>
       </c>
       <c r="C5">
-        <v>13.498</v>
+        <v>17.894</v>
       </c>
       <c r="D5">
-        <v>0.057</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>198.651</v>
+        <v>195.679</v>
       </c>
       <c r="C6">
-        <v>13.498</v>
+        <v>17.894</v>
       </c>
       <c r="D6">
-        <v>0.068</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>50.225</v>
+        <v>51.851</v>
       </c>
       <c r="C7">
-        <v>1.942</v>
+        <v>2.327</v>
       </c>
       <c r="D7">
-        <v>0.039</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,13 +510,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>49.775</v>
+        <v>48.149</v>
       </c>
       <c r="C8">
-        <v>1.942</v>
+        <v>2.327</v>
       </c>
       <c r="D8">
-        <v>0.039</v>
+        <v>0.048</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>239.321</v>
+        <v>239.327</v>
       </c>
       <c r="C5">
-        <v>17.894</v>
+        <v>17.902</v>
       </c>
       <c r="D5">
         <v>0.075</v>
@@ -482,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>195.679</v>
+        <v>195.673</v>
       </c>
       <c r="C6">
-        <v>17.894</v>
+        <v>17.902</v>
       </c>
       <c r="D6">
         <v>0.091</v>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>239.327</v>
+        <v>239.321</v>
       </c>
       <c r="C5">
-        <v>17.902</v>
+        <v>17.894</v>
       </c>
       <c r="D5">
         <v>0.075</v>
@@ -482,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>195.673</v>
+        <v>195.679</v>
       </c>
       <c r="C6">
-        <v>17.902</v>
+        <v>17.894</v>
       </c>
       <c r="D6">
         <v>0.091</v>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>239.327</v>
+        <v>239.332</v>
       </c>
       <c r="C5">
-        <v>17.902</v>
+        <v>17.909</v>
       </c>
       <c r="D5">
         <v>0.075</v>
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>195.673</v>
+        <v>195.668</v>
       </c>
       <c r="C6">
-        <v>17.902</v>
+        <v>17.909</v>
       </c>
       <c r="D6">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="7" spans="1:4">

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>52.463</v>
+        <v>52.456</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>44.62</v>
+        <v>44.627</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>239.332</v>
+        <v>240.774</v>
       </c>
       <c r="C5">
-        <v>17.909</v>
+        <v>18.32</v>
       </c>
       <c r="D5">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>195.668</v>
+        <v>194.226</v>
       </c>
       <c r="C6">
-        <v>17.909</v>
+        <v>18.32</v>
       </c>
       <c r="D6">
-        <v>0.092</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>51.851</v>
+        <v>51.945</v>
       </c>
       <c r="C7">
-        <v>2.327</v>
+        <v>2.251</v>
       </c>
       <c r="D7">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,13 +510,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>48.149</v>
+        <v>48.055</v>
       </c>
       <c r="C8">
-        <v>2.327</v>
+        <v>2.251</v>
       </c>
       <c r="D8">
-        <v>0.048</v>
+        <v>0.047</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>52.456</v>
+        <v>52.326</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>44.627</v>
+        <v>44.757</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>240.774</v>
+        <v>240.127</v>
       </c>
       <c r="C5">
-        <v>18.32</v>
+        <v>18.146</v>
       </c>
       <c r="D5">
         <v>0.076</v>
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>194.226</v>
+        <v>194.873</v>
       </c>
       <c r="C6">
-        <v>18.32</v>
+        <v>18.146</v>
       </c>
       <c r="D6">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>51.945</v>
+        <v>52.019</v>
       </c>
       <c r="C7">
-        <v>2.251</v>
+        <v>2.267</v>
       </c>
       <c r="D7">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,10 +510,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>48.055</v>
+        <v>47.981</v>
       </c>
       <c r="C8">
-        <v>2.251</v>
+        <v>2.267</v>
       </c>
       <c r="D8">
         <v>0.047</v>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -468,10 +468,10 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>240.127</v>
+        <v>240.65</v>
       </c>
       <c r="C5">
-        <v>18.146</v>
+        <v>18.33</v>
       </c>
       <c r="D5">
         <v>0.076</v>
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>194.873</v>
+        <v>194.35</v>
       </c>
       <c r="C6">
-        <v>18.146</v>
+        <v>18.33</v>
       </c>
       <c r="D6">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="7" spans="1:4">

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>52.326</v>
+        <v>52.64</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>44.757</v>
+        <v>44.443</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>240.65</v>
+        <v>242.093</v>
       </c>
       <c r="C5">
-        <v>18.33</v>
+        <v>18.786</v>
       </c>
       <c r="D5">
-        <v>0.076</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,13 +482,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>194.35</v>
+        <v>192.907</v>
       </c>
       <c r="C6">
-        <v>18.33</v>
+        <v>18.786</v>
       </c>
       <c r="D6">
-        <v>0.094</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>52.019</v>
+        <v>52.123</v>
       </c>
       <c r="C7">
-        <v>2.267</v>
+        <v>2.344</v>
       </c>
       <c r="D7">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,13 +510,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>47.981</v>
+        <v>47.877</v>
       </c>
       <c r="C8">
-        <v>2.267</v>
+        <v>2.344</v>
       </c>
       <c r="D8">
-        <v>0.047</v>
+        <v>0.049</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -496,10 +496,10 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>52.123</v>
+        <v>52.168</v>
       </c>
       <c r="C7">
-        <v>2.344</v>
+        <v>2.348</v>
       </c>
       <c r="D7">
         <v>0.045</v>
@@ -510,10 +510,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>47.877</v>
+        <v>47.832</v>
       </c>
       <c r="C8">
-        <v>2.344</v>
+        <v>2.348</v>
       </c>
       <c r="D8">
         <v>0.049</v>

--- a/outputs/Block6C_Variability_Metrics.xlsx
+++ b/outputs/Block6C_Variability_Metrics.xlsx
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>52.64</v>
+        <v>52.488</v>
       </c>
       <c r="C2">
         <v>1.487</v>
@@ -440,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>44.443</v>
+        <v>44.595</v>
       </c>
       <c r="C3">
         <v>1.243</v>
@@ -468,13 +468,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>242.093</v>
+        <v>243.082</v>
       </c>
       <c r="C5">
-        <v>18.786</v>
+        <v>18.575</v>
       </c>
       <c r="D5">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -482,10 +482,10 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>192.907</v>
+        <v>191.918</v>
       </c>
       <c r="C6">
-        <v>18.786</v>
+        <v>18.575</v>
       </c>
       <c r="D6">
         <v>0.097</v>
@@ -496,13 +496,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>52.168</v>
+        <v>51.414</v>
       </c>
       <c r="C7">
-        <v>2.348</v>
+        <v>2.397</v>
       </c>
       <c r="D7">
-        <v>0.045</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -510,10 +510,10 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>47.832</v>
+        <v>48.586</v>
       </c>
       <c r="C8">
-        <v>2.348</v>
+        <v>2.397</v>
       </c>
       <c r="D8">
         <v>0.049</v>
